--- a/test-data/QA_Test_Cases_Results.xlsx
+++ b/test-data/QA_Test_Cases_Results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="546">
   <si>
     <t>Test Case Template for Project</t>
   </si>
@@ -387,9 +387,6 @@
     <t>Verify that with a valid Indian phone number, the system should validate and accept the input.</t>
   </si>
   <si>
-    <t>Verify that a valid Indian mobile should be accepted and preserved; note any reformatting between entry (+91 88888-88888) and review (+918888888888).</t>
-  </si>
-  <si>
     <t>Test identity: test test / test@test.com / +91 8888888888. FL-010: entry format '+91 88888-88888' collapses to '+918888888888' in review.</t>
   </si>
   <si>
@@ -439,6 +436,12 @@
   </si>
   <si>
     <t>Verify that on payment success, the system should generate a unique Booking ID and a confirmation.</t>
+  </si>
+  <si>
+    <t>Skipped / Fixme: See code for reason.</t>
+  </si>
+  <si>
+    <t>Skipped</t>
   </si>
   <si>
     <t>MTW-SCN-16</t>
@@ -1090,9 +1093,6 @@
     <t>Verify that on payment success, the system should produce exactly one booking reference and matching email/SMS notifications.</t>
   </si>
   <si>
-    <t>Not Executed - Requires payment sandbox and explicit authorization.</t>
-  </si>
-  <si>
     <t>Order ID observed in PayU flow, e.g. MTPAYU_4c3b3ce733f2258874.</t>
   </si>
   <si>
@@ -1262,9 +1262,6 @@
     <t>Verify that on tapping Search with no location, the system should display a clear inline validation message on the Where field.</t>
   </si>
   <si>
-    <t>Inline error 'Please enter a location' displayed under the Where field.</t>
-  </si>
-  <si>
     <t>MTW-SCN-32</t>
   </si>
   <si>
@@ -1469,7 +1466,10 @@
     <t>Verify that 'Visit Help Center' should open a working Help Center page.</t>
   </si>
   <si>
-    <t>Link navigates to helpdesk.mytravaly.com/portal/en/kb which returns 'Sorry! The requested URL was not found.' (404).</t>
+    <t>Error: [2mexpect([22m[31mlocator[39m[2m).not.[22mtoBeVisible[2m([22m[2m)[22m failed</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
   <si>
     <t>Broken link on a valid navigation path; support content is unreachable.</t>
@@ -1496,7 +1496,7 @@
     <t>Verify that with a stay length beyond the maximum allowed nights, the system should reject the range and show a validation message.</t>
   </si>
   <si>
-    <t>System accepts any range; the 5-year stay proceeds with no upper bound enforced.</t>
+    <t>Error: [2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m([22m[2m)[22m failed</t>
   </si>
   <si>
     <t>MTW-SCN-41</t>
@@ -1519,9 +1519,6 @@
     <t>Verify that with a guest aged 17y 11m, the system should classify the guest as CHILD per a defined boundary rule.</t>
   </si>
   <si>
-    <t>Boundary at 17y 11m is undefined; the guest can be misclassified as an adult.</t>
-  </si>
-  <si>
     <t>MTW-SCN-42</t>
   </si>
   <si>
@@ -1540,9 +1537,6 @@
   </si>
   <si>
     <t>Verify that on repeated search clicks, the system should keep the selected date range constant.</t>
-  </si>
-  <si>
-    <t>Each click shifts both check-in and check-out back by one day (visible in checkin/checkout URL params).</t>
   </si>
   <si>
     <t>Precondition: Where, When and Who must all be filled before a search can run (see MTW-TC-03).</t>
@@ -1569,9 +1563,6 @@
     <t>Verify that the Search control state should be consistent: a control rendered as disabled should not fire handlers, or the control should be enabled and rely on validation messaging instead.</t>
   </si>
   <si>
-    <t>Button appears greyed out/disabled yet still fires validation on tap - the visual state and the interactive behaviour disagree.</t>
-  </si>
-  <si>
     <t>Ambiguous state: users may read grey as 'not ready' and never tap to discover the reason.</t>
   </si>
   <si>
@@ -1595,9 +1586,6 @@
     <t>Verify that with a check-in date that expires during the hold, the server should re-validate at submission and block the now-past date.</t>
   </si>
   <si>
-    <t>Booking proceeds for a past check-in date; no re-validation is performed at submission.</t>
-  </si>
-  <si>
     <t>MTW-SCN-45</t>
   </si>
   <si>
@@ -1618,7 +1606,7 @@
     <t>Verify that on page refresh the timer should continue from the server-side expiry, and on timeout the room should release and retry should work without a crash.</t>
   </si>
   <si>
-    <t>Timer resets to 10:00 on every refresh; on timeout, retry crashes with 'Unable to load payment method'.</t>
+    <t>Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoContain[2m([22m[32mexpected[39m[2m) // indexOf[22m</t>
   </si>
   <si>
     <t>Distinct from MTW-TC-72: this is timer reset on refresh; TC-72 is controls left enabled after expiry.</t>
@@ -1643,7 +1631,7 @@
     <t>Verify that with a structurally invalid email address, the system should reject it and display a validation error.</t>
   </si>
   <si>
-    <t>Email is accepted because only the presence of '@' and '.' is checked.</t>
+    <t>Error: [2mexpect([22m[31mlocator[39m[2m).[22mtoContainText[2m([22m[32mexpected[39m[2m)[22m failed</t>
   </si>
   <si>
     <t>CONFLICT: automation TC3 reports Pass for invalid email. Manual test used a structurally valid but non-existent domain (asdsgsi@sdhd.dj). Reconcile scope before sign-off.</t>
@@ -1669,7 +1657,7 @@
     <t>Verify that with text beyond the allowed length, the system should cap input on the client and reject it on the server with an error.</t>
   </si>
   <si>
-    <t>Unlimited-length text is accepted; no maxlength constraint or server-side length validation exists.</t>
+    <t>Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoBeLessThan[2m([22m[32mexpected[39m[2m)[22m</t>
   </si>
   <si>
     <t>MTW-SCN-48</t>
@@ -1692,7 +1680,7 @@
     <t>Verify that with the GREATSTAY coupon, the system should apply 40% off the original base price, giving a final total of ~₹765.89.</t>
   </si>
   <si>
-    <t>Base price is inflated to ₹1,620.38 first; final payable ≈ ₹1,078.20 — a near-zero real saving (deceptive pricing).</t>
+    <t>Error: locator.scrollIntoViewIfNeeded: Element is not attached to the DOM</t>
   </si>
   <si>
     <t>MTW-SCN-49</t>
@@ -1716,7 +1704,7 @@
     <t>Verify that payment selectors should be keyboard-focusable with accessible names, visible focus states, keyboard activation and a selected state.</t>
   </si>
   <si>
-    <t>Selectors are clickable DIV elements with no role, tabindex or keyboard semantics.</t>
+    <t>Skipped via Automation: Test execution skipped per user instructions.</t>
   </si>
   <si>
     <t>MTW-SCN-50</t>
@@ -1739,9 +1727,6 @@
     <t>Verify that mobile navigation controls should expose unique accessible names such as 'Open menu' and 'Close menu'.</t>
   </si>
   <si>
-    <t>The menu and close controls were exposed as unnamed buttons.</t>
-  </si>
-  <si>
     <t>MTW-SCN-51</t>
   </si>
   <si>
@@ -1762,7 +1747,7 @@
     <t>Verify that meaningful images should carry concise unique alternative text and decorative images should use empty alt text.</t>
   </si>
   <si>
-    <t>Images used generic labels such as 'Property', 'Guestroom' or repeated room names.</t>
+    <t>Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoMatch[2m([22m[32mexpected[39m[2m)[22m</t>
   </si>
   <si>
     <t>MTW-SCN-52</t>
@@ -1786,9 +1771,6 @@
     <t>Verify that on continuing to checkout, the system should preserve the exact selected room name, occupancy and rate.</t>
   </si>
   <si>
-    <t>Checkout displayed '1 room: Superior room, 1 king bed' instead of the selected Vaidik Cottages.</t>
-  </si>
-  <si>
     <t>MTW-SCN-53</t>
   </si>
   <si>
@@ -1810,9 +1792,6 @@
     <t>Verify that promotional-email consent should be opt-in by default and the declaration should accurately describe the behaviour.</t>
   </si>
   <si>
-    <t>Promotional emails are enabled by default while the page states 'We do not send promotional emails'.</t>
-  </si>
-  <si>
     <t>MTW-SCN-54</t>
   </si>
   <si>
@@ -1830,9 +1809,6 @@
   </si>
   <si>
     <t>Verify that all currency values should display consistently to two decimal places (e.g. INR 4,990.50, not 4,990.5).</t>
-  </si>
-  <si>
-    <t>Some totals appeared as INR 4,990.5 and 490.5 rather than two decimal places.</t>
   </si>
 </sst>
 </file>
@@ -2145,7 +2121,7 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3515,16 +3491,16 @@
         <v>114</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J24" s="16" t="s">
         <v>33</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L24" s="20" t="s">
         <v>35</v>
@@ -3547,36 +3523,38 @@
     </row>
     <row r="25" ht="143" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="22" t="s">
         <v>117</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>118</v>
       </c>
       <c r="C25" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D25" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="F25" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="G25" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="G25" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="22"/>
+      <c r="H25" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I25" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J25" s="22"/>
       <c r="K25" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="L25" s="30" t="s">
         <v>123</v>
-      </c>
-      <c r="L25" s="30" t="s">
-        <v>124</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10"/>
@@ -3596,29 +3574,31 @@
     </row>
     <row r="26" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="16" t="s">
         <v>125</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>126</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="F26" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="G26" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="H26" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H26" s="16"/>
       <c r="I26" s="24" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J26" s="16"/>
       <c r="K26" s="19"/>
@@ -3643,33 +3623,35 @@
     </row>
     <row r="27" ht="260" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C27" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="H27" s="22"/>
+        <v>137</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I27" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J27" s="22"/>
       <c r="K27" s="25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L27" s="28" t="s">
         <v>35</v>
@@ -3692,29 +3674,31 @@
     </row>
     <row r="28" ht="102.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="H28" s="16"/>
+        <v>145</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I28" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J28" s="16"/>
       <c r="K28" s="19"/>
@@ -3739,33 +3723,35 @@
     </row>
     <row r="29" ht="197" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="H29" s="22"/>
+        <v>152</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I29" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J29" s="22"/>
       <c r="K29" s="25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L29" s="26" t="s">
         <v>42</v>
@@ -3788,33 +3774,35 @@
     </row>
     <row r="30" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="H30" s="16"/>
+        <v>159</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I30" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J30" s="16"/>
       <c r="K30" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L30" s="29" t="s">
         <v>42</v>
@@ -3837,33 +3825,35 @@
     </row>
     <row r="31" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="H31" s="22"/>
+        <v>166</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I31" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J31" s="22"/>
       <c r="K31" s="25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L31" s="26" t="s">
         <v>42</v>
@@ -3886,37 +3876,37 @@
     </row>
     <row r="32" ht="102.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L32" s="27" t="s">
         <v>50</v>
@@ -3939,37 +3929,37 @@
     </row>
     <row r="33" ht="89" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K33" s="25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L33" s="28" t="s">
         <v>35</v>
@@ -3992,37 +3982,37 @@
     </row>
     <row r="34" ht="170" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J34" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L34" s="20" t="s">
         <v>35</v>
@@ -4045,37 +4035,37 @@
     </row>
     <row r="35" ht="102.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J35" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K35" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L35" s="26" t="s">
         <v>42</v>
@@ -4098,37 +4088,37 @@
     </row>
     <row r="36" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J36" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L36" s="20" t="s">
         <v>35</v>
@@ -4151,37 +4141,37 @@
     </row>
     <row r="37" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J37" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K37" s="25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L37" s="28" t="s">
         <v>35</v>
@@ -4204,37 +4194,37 @@
     </row>
     <row r="38" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J38" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K38" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L38" s="27" t="s">
         <v>50</v>
@@ -4257,37 +4247,37 @@
     </row>
     <row r="39" ht="102.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I39" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K39" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L39" s="34" t="s">
         <v>50</v>
@@ -4310,37 +4300,37 @@
     </row>
     <row r="40" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I40" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J40" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L40" s="20" t="s">
         <v>35</v>
@@ -4363,37 +4353,37 @@
     </row>
     <row r="41" ht="89" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I41" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K41" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L41" s="28" t="s">
         <v>35</v>
@@ -4416,37 +4406,37 @@
     </row>
     <row r="42" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="H42" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>244</v>
       </c>
       <c r="I42" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J42" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L42" s="20" t="s">
         <v>35</v>
@@ -4469,37 +4459,37 @@
     </row>
     <row r="43" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I43" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K43" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L43" s="26" t="s">
         <v>42</v>
@@ -4522,37 +4512,37 @@
     </row>
     <row r="44" ht="89" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I44" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J44" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K44" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L44" s="27" t="s">
         <v>50</v>
@@ -4575,37 +4565,37 @@
     </row>
     <row r="45" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I45" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K45" s="25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L45" s="34" t="s">
         <v>50</v>
@@ -4628,37 +4618,37 @@
     </row>
     <row r="46" ht="102.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I46" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J46" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K46" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L46" s="20" t="s">
         <v>35</v>
@@ -4681,37 +4671,37 @@
     </row>
     <row r="47" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I47" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K47" s="25" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L47" s="28" t="s">
         <v>35</v>
@@ -4734,37 +4724,37 @@
     </row>
     <row r="48" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I48" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L48" s="29" t="s">
         <v>42</v>
@@ -4787,37 +4777,37 @@
     </row>
     <row r="49" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I49" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K49" s="25" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L49" s="26" t="s">
         <v>42</v>
@@ -4840,25 +4830,25 @@
     </row>
     <row r="50" ht="89" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>31</v>
@@ -4867,10 +4857,10 @@
         <v>32</v>
       </c>
       <c r="J50" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L50" s="27" t="s">
         <v>50</v>
@@ -4893,25 +4883,25 @@
     </row>
     <row r="51" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H51" s="22" t="s">
         <v>31</v>
@@ -4920,10 +4910,10 @@
         <v>32</v>
       </c>
       <c r="J51" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K51" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L51" s="34" t="s">
         <v>50</v>
@@ -4946,29 +4936,31 @@
     </row>
     <row r="52" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="35" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="H52" s="16"/>
+        <v>318</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>130</v>
+      </c>
       <c r="I52" s="24" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J52" s="16"/>
       <c r="K52" s="19"/>
@@ -4993,29 +4985,31 @@
     </row>
     <row r="53" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="35" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>323</v>
-      </c>
-      <c r="H53" s="22"/>
+        <v>324</v>
+      </c>
+      <c r="H53" s="22" t="s">
+        <v>130</v>
+      </c>
       <c r="I53" s="24" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J53" s="22"/>
       <c r="K53" s="25"/>
@@ -5040,38 +5034,38 @@
     </row>
     <row r="54" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>330</v>
+        <v>130</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J54" s="16"/>
       <c r="K54" s="19" t="s">
         <v>331</v>
       </c>
       <c r="L54" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M54" s="21"/>
       <c r="N54" s="21"/>
@@ -5111,9 +5105,11 @@
       <c r="G55" s="22" t="s">
         <v>337</v>
       </c>
-      <c r="H55" s="22"/>
+      <c r="H55" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I55" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J55" s="22"/>
       <c r="K55" s="25"/>
@@ -5158,9 +5154,11 @@
       <c r="G56" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="H56" s="16"/>
+      <c r="H56" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I56" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J56" s="16"/>
       <c r="K56" s="19"/>
@@ -5203,9 +5201,11 @@
       <c r="G57" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="H57" s="22"/>
+      <c r="H57" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I57" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J57" s="22"/>
       <c r="K57" s="25"/>
@@ -5248,9 +5248,11 @@
       <c r="G58" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="H58" s="16"/>
+      <c r="H58" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I58" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J58" s="16"/>
       <c r="K58" s="19"/>
@@ -5293,9 +5295,11 @@
       <c r="G59" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="H59" s="22"/>
+      <c r="H59" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I59" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J59" s="22"/>
       <c r="K59" s="25"/>
@@ -5338,9 +5342,11 @@
       <c r="G60" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="H60" s="16"/>
+      <c r="H60" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I60" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J60" s="16"/>
       <c r="K60" s="19"/>
@@ -5464,10 +5470,10 @@
         <v>379</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>380</v>
+        <v>31</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J63" s="22" t="s">
         <v>33</v>
@@ -5494,29 +5500,31 @@
     </row>
     <row r="64" ht="116" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B64" s="16" t="s">
         <v>381</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>382</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D64" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="E64" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="E64" s="16" t="s">
+      <c r="F64" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="F64" s="16" t="s">
+      <c r="G64" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="G64" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="H64" s="16"/>
+      <c r="H64" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I64" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J64" s="16"/>
       <c r="K64" s="19"/>
@@ -5541,37 +5549,37 @@
     </row>
     <row r="65" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="B65" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="C65" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D65" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="C65" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="D65" s="15" t="s">
+      <c r="E65" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="F65" s="22" t="s">
         <v>390</v>
       </c>
-      <c r="F65" s="22" t="s">
+      <c r="G65" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="G65" s="22" t="s">
+      <c r="H65" s="22" t="s">
         <v>392</v>
-      </c>
-      <c r="H65" s="22" t="s">
-        <v>393</v>
       </c>
       <c r="I65" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J65" s="22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L65" s="28" t="s">
         <v>35</v>
@@ -5594,37 +5602,37 @@
     </row>
     <row r="66" ht="89" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="B66" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="C66" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D66" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="C66" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D66" s="15" t="s">
+      <c r="E66" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="F66" s="16" t="s">
         <v>397</v>
       </c>
-      <c r="F66" s="16" t="s">
+      <c r="G66" s="16" t="s">
         <v>398</v>
       </c>
-      <c r="G66" s="16" t="s">
+      <c r="H66" s="16" t="s">
         <v>399</v>
-      </c>
-      <c r="H66" s="16" t="s">
-        <v>400</v>
       </c>
       <c r="I66" s="18" t="s">
         <v>23</v>
       </c>
       <c r="J66" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L66" s="29" t="s">
         <v>42</v>
@@ -5647,29 +5655,31 @@
     </row>
     <row r="67" ht="62" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="B67" s="22" t="s">
         <v>402</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="C67" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="D67" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="C67" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="D67" s="15" t="s">
+      <c r="E67" s="22" t="s">
         <v>404</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="F67" s="22" t="s">
         <v>405</v>
       </c>
-      <c r="F67" s="22" t="s">
+      <c r="G67" s="22" t="s">
         <v>406</v>
       </c>
-      <c r="G67" s="22" t="s">
-        <v>407</v>
-      </c>
-      <c r="H67" s="22"/>
+      <c r="H67" s="22" t="s">
+        <v>130</v>
+      </c>
       <c r="I67" s="24" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J67" s="22"/>
       <c r="K67" s="25"/>
@@ -5694,29 +5704,31 @@
     </row>
     <row r="68" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="B68" s="16" t="s">
         <v>408</v>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>409</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E68" s="16" t="s">
         <v>112</v>
       </c>
       <c r="F68" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="G68" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="G68" s="16" t="s">
-        <v>412</v>
-      </c>
-      <c r="H68" s="16"/>
+      <c r="H68" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I68" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J68" s="16"/>
       <c r="K68" s="19"/>
@@ -5741,29 +5753,31 @@
     </row>
     <row r="69" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="B69" s="22" t="s">
         <v>413</v>
-      </c>
-      <c r="B69" s="22" t="s">
-        <v>414</v>
       </c>
       <c r="C69" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D69" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="E69" s="22" t="s">
         <v>415</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="F69" s="22" t="s">
         <v>416</v>
       </c>
-      <c r="F69" s="22" t="s">
+      <c r="G69" s="22" t="s">
         <v>417</v>
       </c>
-      <c r="G69" s="22" t="s">
-        <v>418</v>
-      </c>
-      <c r="H69" s="22"/>
+      <c r="H69" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I69" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J69" s="22"/>
       <c r="K69" s="25"/>
@@ -5788,29 +5802,31 @@
     </row>
     <row r="70" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B70" s="16" t="s">
         <v>419</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>420</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D70" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="E70" s="16" t="s">
         <v>421</v>
       </c>
-      <c r="E70" s="16" t="s">
+      <c r="F70" s="16" t="s">
         <v>422</v>
       </c>
-      <c r="F70" s="16" t="s">
+      <c r="G70" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="G70" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="H70" s="16"/>
+      <c r="H70" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I70" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J70" s="16"/>
       <c r="K70" s="19"/>
@@ -5835,34 +5851,36 @@
     </row>
     <row r="71" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="B71" s="22" t="s">
         <v>425</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>426</v>
       </c>
       <c r="C71" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D71" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="E71" s="22" t="s">
         <v>427</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="F71" s="22" t="s">
         <v>428</v>
       </c>
-      <c r="F71" s="22" t="s">
+      <c r="G71" s="22" t="s">
         <v>429</v>
       </c>
-      <c r="G71" s="22" t="s">
-        <v>430</v>
-      </c>
-      <c r="H71" s="22"/>
+      <c r="H71" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="I71" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J71" s="22"/>
       <c r="K71" s="25"/>
       <c r="L71" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10"/>
@@ -5882,34 +5900,36 @@
     </row>
     <row r="72" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B72" s="16" t="s">
         <v>431</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>432</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D72" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="E72" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="F72" s="16" t="s">
         <v>434</v>
       </c>
-      <c r="F72" s="16" t="s">
+      <c r="G72" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="G72" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="H72" s="16"/>
+      <c r="H72" s="16" t="s">
+        <v>31</v>
+      </c>
       <c r="I72" s="24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J72" s="16"/>
       <c r="K72" s="19"/>
       <c r="L72" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M72" s="21"/>
       <c r="N72" s="21"/>
@@ -5960,31 +5980,31 @@
     </row>
     <row r="74" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="B74" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="C74" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D74" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="C74" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="D74" s="15" t="s">
+      <c r="E74" s="16" t="s">
         <v>439</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="F74" s="16" t="s">
         <v>440</v>
       </c>
-      <c r="F74" s="16" t="s">
+      <c r="G74" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="G74" s="16" t="s">
+      <c r="H74" s="16" t="s">
         <v>442</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="I74" s="39" t="s">
         <v>443</v>
-      </c>
-      <c r="I74" s="39" t="s">
-        <v>23</v>
       </c>
       <c r="J74" s="16"/>
       <c r="K74" s="19" t="s">
@@ -6035,7 +6055,7 @@
         <v>451</v>
       </c>
       <c r="I75" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J75" s="22" t="s">
         <v>33</v>
@@ -6083,10 +6103,10 @@
         <v>457</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>458</v>
+        <v>130</v>
       </c>
       <c r="I76" s="39" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J76" s="16" t="s">
         <v>33</v>
@@ -6113,37 +6133,37 @@
     </row>
     <row r="77" ht="89" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B77" s="22" t="s">
         <v>459</v>
-      </c>
-      <c r="B77" s="22" t="s">
-        <v>460</v>
       </c>
       <c r="C77" s="23" t="s">
         <v>26</v>
       </c>
       <c r="D77" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="E77" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="F77" s="22" t="s">
         <v>462</v>
       </c>
-      <c r="F77" s="22" t="s">
+      <c r="G77" s="22" t="s">
         <v>463</v>
       </c>
-      <c r="G77" s="22" t="s">
-        <v>464</v>
-      </c>
       <c r="H77" s="22" t="s">
-        <v>465</v>
+        <v>130</v>
       </c>
       <c r="I77" s="39" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J77" s="22" t="s">
         <v>33</v>
       </c>
       <c r="K77" s="25" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="L77" s="34" t="s">
         <v>50</v>
@@ -6166,37 +6186,37 @@
     </row>
     <row r="78" ht="102.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="33" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C78" s="17" t="s">
         <v>26</v>
       </c>
       <c r="D78" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="F78" s="16" t="s">
         <v>469</v>
       </c>
-      <c r="E78" s="16" t="s">
+      <c r="G78" s="16" t="s">
         <v>470</v>
       </c>
-      <c r="F78" s="16" t="s">
-        <v>471</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>472</v>
-      </c>
       <c r="H78" s="16" t="s">
-        <v>473</v>
+        <v>130</v>
       </c>
       <c r="I78" s="39" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J78" s="16" t="s">
         <v>33</v>
       </c>
       <c r="K78" s="19" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="L78" s="20" t="s">
         <v>35</v>
@@ -6219,38 +6239,38 @@
     </row>
     <row r="79" ht="156.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C79" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D79" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="F79" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="G79" s="22" t="s">
         <v>477</v>
       </c>
-      <c r="E79" s="22" t="s">
-        <v>478</v>
-      </c>
-      <c r="F79" s="22" t="s">
-        <v>479</v>
-      </c>
-      <c r="G79" s="22" t="s">
-        <v>480</v>
-      </c>
       <c r="H79" s="22" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="I79" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J79" s="22" t="s">
         <v>33</v>
       </c>
       <c r="K79" s="25"/>
       <c r="L79" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10"/>
@@ -6270,37 +6290,37 @@
     </row>
     <row r="80" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C80" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D80" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="H80" s="16" t="s">
         <v>484</v>
       </c>
-      <c r="E80" s="16" t="s">
-        <v>485</v>
-      </c>
-      <c r="F80" s="16" t="s">
-        <v>486</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>487</v>
-      </c>
-      <c r="H80" s="16" t="s">
-        <v>488</v>
-      </c>
       <c r="I80" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J80" s="16" t="s">
         <v>33</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="L80" s="27" t="s">
         <v>50</v>
@@ -6323,37 +6343,37 @@
     </row>
     <row r="81" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C81" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D81" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="G81" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="H81" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="E81" s="22" t="s">
-        <v>493</v>
-      </c>
-      <c r="F81" s="22" t="s">
-        <v>494</v>
-      </c>
-      <c r="G81" s="22" t="s">
-        <v>495</v>
-      </c>
-      <c r="H81" s="22" t="s">
-        <v>496</v>
-      </c>
       <c r="I81" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J81" s="22" t="s">
         <v>33</v>
       </c>
       <c r="K81" s="25" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="L81" s="28" t="s">
         <v>35</v>
@@ -6376,31 +6396,31 @@
     </row>
     <row r="82" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C82" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D82" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="H82" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="E82" s="16" t="s">
-        <v>501</v>
-      </c>
-      <c r="F82" s="16" t="s">
-        <v>502</v>
-      </c>
-      <c r="G82" s="16" t="s">
-        <v>503</v>
-      </c>
-      <c r="H82" s="16" t="s">
-        <v>504</v>
-      </c>
       <c r="I82" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J82" s="16" t="s">
         <v>33</v>
@@ -6427,38 +6447,38 @@
     </row>
     <row r="83" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C83" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D83" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="E83" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="F83" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="G83" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="H83" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="E83" s="22" t="s">
-        <v>508</v>
-      </c>
-      <c r="F83" s="22" t="s">
-        <v>509</v>
-      </c>
-      <c r="G83" s="22" t="s">
-        <v>510</v>
-      </c>
-      <c r="H83" s="22" t="s">
-        <v>511</v>
-      </c>
       <c r="I83" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J83" s="22" t="s">
         <v>33</v>
       </c>
       <c r="K83" s="25"/>
       <c r="L83" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10"/>
@@ -6478,31 +6498,31 @@
     </row>
     <row r="84" ht="143" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C84" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D84" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="H84" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="E84" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="F84" s="16" t="s">
-        <v>516</v>
-      </c>
-      <c r="G84" s="16" t="s">
-        <v>517</v>
-      </c>
-      <c r="H84" s="16" t="s">
-        <v>518</v>
-      </c>
       <c r="I84" s="39" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J84" s="16" t="s">
         <v>33</v>
@@ -6529,31 +6549,31 @@
     </row>
     <row r="85" ht="75.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="F85" s="22" t="s">
         <v>519</v>
       </c>
-      <c r="B85" s="22" t="s">
+      <c r="G85" s="22" t="s">
         <v>520</v>
       </c>
-      <c r="C85" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>521</v>
-      </c>
-      <c r="E85" s="22" t="s">
-        <v>522</v>
-      </c>
-      <c r="F85" s="22" t="s">
-        <v>523</v>
-      </c>
-      <c r="G85" s="22" t="s">
-        <v>524</v>
-      </c>
       <c r="H85" s="22" t="s">
-        <v>525</v>
+        <v>130</v>
       </c>
       <c r="I85" s="39" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J85" s="22" t="s">
         <v>33</v>
@@ -6580,31 +6600,31 @@
     </row>
     <row r="86" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C86" s="17" t="s">
         <v>91</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="I86" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J86" s="16" t="s">
         <v>33</v>
@@ -6631,38 +6651,38 @@
     </row>
     <row r="87" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C87" s="23" t="s">
         <v>91</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F87" s="22" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>539</v>
+        <v>484</v>
       </c>
       <c r="I87" s="39" t="s">
-        <v>23</v>
+        <v>443</v>
       </c>
       <c r="J87" s="22" t="s">
         <v>33</v>
       </c>
       <c r="K87" s="25"/>
       <c r="L87" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10"/>
@@ -6682,31 +6702,31 @@
     </row>
     <row r="88" ht="143" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C88" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>546</v>
+        <v>130</v>
       </c>
       <c r="I88" s="15" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J88" s="16" t="s">
         <v>33</v>
@@ -6733,31 +6753,31 @@
     </row>
     <row r="89" ht="129.5" customHeight="1" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C89" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="F89" s="22" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="H89" s="22" t="s">
-        <v>553</v>
+        <v>130</v>
       </c>
       <c r="I89" s="15" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="J89" s="22" t="s">
         <v>33</v>
@@ -11397,8 +11417,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="I12:I89">
-      <formula1>"Pass,Fail,Not Executed,Blocked"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="I11:I89">
+      <formula1>"Pass,Fail,Skipped,Not Executed,Blocked"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="L12:L89">
       <formula1>"Critical,High,Medium,Low"</formula1>

--- a/test-data/QA_Test_Cases_Results.xlsx
+++ b/test-data/QA_Test_Cases_Results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="587">
   <si>
     <t>Test Case Template for Project</t>
   </si>
@@ -1832,7 +1832,7 @@
     <t/>
   </si>
   <si>
-    <t>■  EXTENDED UI &amp; SEO TESTS  —  Verifying auxiliary features (6 cases)</t>
+    <t>■  EXTENDED UI &amp; SEO TESTS  —  Verifying auxiliary features (5 cases)</t>
   </si>
   <si>
     <t>MTW-EXT-01</t>
@@ -1877,31 +1877,16 @@
     <t>Dropdown opens</t>
   </si>
   <si>
-    <t>MTW-EXT-03</t>
-  </si>
-  <si>
-    <t>Newsletter subscription</t>
-  </si>
-  <si>
-    <t>MTW-TC-57</t>
+    <t>MTW-EXT-04</t>
+  </si>
+  <si>
+    <t>Footer social media links</t>
+  </si>
+  <si>
+    <t>MTW-TC-58</t>
   </si>
   <si>
     <t>User scrolls to footer</t>
-  </si>
-  <si>
-    <t>Test newsletter subscription input</t>
-  </si>
-  <si>
-    <t>Can subscribe</t>
-  </si>
-  <si>
-    <t>MTW-EXT-04</t>
-  </si>
-  <si>
-    <t>Footer social media links</t>
-  </si>
-  <si>
-    <t>MTW-TC-58</t>
   </si>
   <si>
     <t>Test Social Media href links</t>
@@ -2612,7 +2597,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA100"/>
+  <dimension ref="A1:AA99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.63"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -7185,19 +7170,19 @@
         <v>575</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>552</v>
@@ -7212,30 +7197,30 @@
         <v>552</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>552</v>
@@ -7250,44 +7235,6 @@
         <v>552</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="L100" s="1" t="s">
         <v>38</v>
       </c>
     </row>

--- a/test-data/QA_Test_Cases_Results.xlsx
+++ b/test-data/QA_Test_Cases_Results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="688">
   <si>
     <t>Test Case Template for Project</t>
   </si>
@@ -131,6 +131,12 @@
     <t>Medium</t>
   </si>
   <si>
+    <t>2528 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:00 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-02</t>
   </si>
   <si>
@@ -151,6 +157,12 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>7109 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:18 PM</t>
   </si>
   <si>
     <t>MTW-SCN-03</t>
@@ -181,6 +193,12 @@
     <t>High</t>
   </si>
   <si>
+    <t>5827 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:21 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-04</t>
   </si>
   <si>
@@ -202,6 +220,12 @@
     <t>When/Who cannot be cleared to empty, so no empty-state validation case applies to them.</t>
   </si>
   <si>
+    <t>3941 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:04 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-05</t>
   </si>
   <si>
@@ -226,6 +250,12 @@
     <t>Blocked if autocomplete fails to return a selectable suggestion - see H_09.7 conflict.</t>
   </si>
   <si>
+    <t>6778 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:27 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-06</t>
   </si>
   <si>
@@ -249,6 +279,12 @@
     <t>Verify that with price, rating, property-type, and amenity filters applied, the system should return accurate matching results.</t>
   </si>
   <si>
+    <t>9237 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:37 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-07</t>
   </si>
   <si>
@@ -269,6 +305,12 @@
     <t>Verify that with each sort option, the system should reorder listings correctly by the chosen criterion.</t>
   </si>
   <si>
+    <t>8976 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:46 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-08</t>
   </si>
   <si>
@@ -289,6 +331,12 @@
     <t>Verify that on reaching the end of results, the system should load the next set without duplicates or gaps.</t>
   </si>
   <si>
+    <t>11938 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:58 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-09</t>
   </si>
   <si>
@@ -309,6 +357,12 @@
     <t>Verify that in map view, the system should plot hotels accurately and link each pin to its listing.</t>
   </si>
   <si>
+    <t>6736 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:11 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-10</t>
   </si>
   <si>
@@ -330,6 +384,12 @@
   </si>
   <si>
     <t>Verify that on the hotel page, the system should display accurate property details, map pin, and check-in/out timings.</t>
+  </si>
+  <si>
+    <t>19092 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:32 PM</t>
   </si>
   <si>
     <t>MTW-SCN-11</t>
@@ -353,6 +413,12 @@
     <t>Verify that the selected room type, meal plan, dates and total payable are accurately preserved into the checkout booking summary.</t>
   </si>
   <si>
+    <t>24727 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:57 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-12</t>
   </si>
   <si>
@@ -373,6 +439,12 @@
     <t>Verify that the aggregate rating displays and 'Show all reviews' opens a modal listing all verified guest reviews.</t>
   </si>
   <si>
+    <t>20047 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:34 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-13</t>
   </si>
   <si>
@@ -397,6 +469,12 @@
   </si>
   <si>
     <t>Test identity: test test / test@test.com / +91 8888888888. FL-010: entry format '+91 88888-88888' collapses to '+918888888888' in review.</t>
+  </si>
+  <si>
+    <t>18908 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:24 PM</t>
   </si>
   <si>
     <t>MTW-SCN-14</t>
@@ -426,6 +504,15 @@
     <t>Critical</t>
   </si>
   <si>
+    <t>25071 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:49 PM</t>
+  </si>
+  <si>
+    <t>Error: [2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m([22m[2m)[22m failed</t>
+  </si>
+  <si>
     <t>MTW-SCN-15</t>
   </si>
   <si>
@@ -451,6 +538,9 @@
   </si>
   <si>
     <t>Skipped</t>
+  </si>
+  <si>
+    <t>222 ms</t>
   </si>
   <si>
     <t>MTW-SCN-16</t>
@@ -478,6 +568,12 @@
     <t>No standalone dashboard on site: profile management occurs in checkout. Automation uses non-blocking popup handling (.catch(() =&gt; page)) and 20,000ms timeouts to wait out the 'Verifying...' spinner.</t>
   </si>
   <si>
+    <t>21257 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:28 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-17</t>
   </si>
   <si>
@@ -499,6 +595,12 @@
   </si>
   <si>
     <t>Verify that clicking 'Add Hotel' opens a new tab and redirects partners to the B2B portal (hbc.mytravaly.com).</t>
+  </si>
+  <si>
+    <t>5522 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:15 PM</t>
   </si>
   <si>
     <t>MTW-SCN-18</t>
@@ -528,6 +630,12 @@
     <t>Corrected: no Contact Us form exists on site; page is static contact info.</t>
   </si>
   <si>
+    <t>2707 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:31 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-19</t>
   </si>
   <si>
@@ -548,6 +656,12 @@
   </si>
   <si>
     <t>Partial overlap with FA_10.1 (visibility only); this case covers expand/collapse interaction.</t>
+  </si>
+  <si>
+    <t>2785 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:34 PM</t>
   </si>
   <si>
     <t>MTW-SCN-20</t>
@@ -571,6 +685,12 @@
   </si>
   <si>
     <t>Narrowed: T&amp;C and Privacy Policy navigation covered by TC_08.4 and TC_08.5.</t>
+  </si>
+  <si>
+    <t>1921 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:36 PM</t>
   </si>
   <si>
     <t>PAY-SCN-01</t>
@@ -598,16 +718,16 @@
     <t>The Pay/Proceed button should be enabled, and clicking it should redirect the user to a payment/checkout/gateway URL (matching payment, checkout, razorpay or pay).</t>
   </si>
   <si>
-    <t>Payment button enabled as expected; page redirected to a URL matching the payment/checkout pattern on all three browsers.</t>
-  </si>
-  <si>
-    <t>Not Executed</t>
-  </si>
-  <si>
     <t>Gontla Alekhya (Automated)</t>
   </si>
   <si>
     <t>Redirection to gateway only. Per-method validation covered by MTW-TC-14.</t>
+  </si>
+  <si>
+    <t>10667 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:55 PM</t>
   </si>
   <si>
     <t>PAY-SCN-05</t>
@@ -629,10 +749,13 @@
     <t>The total amount element should be visible and its text should match the pattern '₹' followed by a numeric value (e.g. ₹1,234).</t>
   </si>
   <si>
-    <t>Total amount element was visible and matched the expected ₹-prefixed numeric pattern on Chromium and Firefox (Webkit not included in this run).</t>
-  </si>
-  <si>
     <t>Also covers former MTW-TC-34 (booking summary total calculation).</t>
+  </si>
+  <si>
+    <t>5497 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:56:26 PM</t>
   </si>
   <si>
     <t>FTR-SCN-01</t>
@@ -659,10 +782,13 @@
     <t>All 15 footer links across the three columns should be visible.</t>
   </si>
   <si>
-    <t>All footer links across all three columns rendered and were visible as expected on all three browsers.</t>
-  </si>
-  <si>
     <t>Executed on Chromium, Firefox &amp; Webkit</t>
+  </si>
+  <si>
+    <t>2781 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:39 PM</t>
   </si>
   <si>
     <t>FTR-SCN-03</t>
@@ -684,7 +810,10 @@
     <t>Each visible social icon's href should point to its correct platform domain.</t>
   </si>
   <si>
-    <t>All visible social icons resolved to the correct platform domains on all three browsers.</t>
+    <t>1223 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:42 PM</t>
   </si>
   <si>
     <t>FTR-SCN-04</t>
@@ -707,10 +836,13 @@
     <t>The resulting page URL (same tab or new tab) should match a Terms/Conditions pattern.</t>
   </si>
   <si>
-    <t>Navigation correctly landed on a Terms &amp; Conditions URL in both same-tab and new-tab scenarios, on all three browsers.</t>
-  </si>
-  <si>
     <t>Also covers T&amp;C navigation formerly bundled in MTW-TC-20.</t>
+  </si>
+  <si>
+    <t>5778 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:48 PM</t>
   </si>
   <si>
     <t>FTR-SCN-05</t>
@@ -733,10 +865,13 @@
     <t>The resulting page URL (same tab or new tab) should contain 'privacy-policy'.</t>
   </si>
   <si>
-    <t>Navigation correctly landed on a URL containing 'privacy-policy' in both same-tab and new-tab scenarios, on all three browsers.</t>
-  </si>
-  <si>
     <t>Also covers Privacy Policy navigation formerly bundled in MTW-TC-20.</t>
+  </si>
+  <si>
+    <t>3627 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:52 PM</t>
   </si>
   <si>
     <t>HOM-SCN-01</t>
@@ -762,6 +897,9 @@
   </si>
   <si>
     <t>All three header elements loaded and were visible as expected on all three browsers.</t>
+  </si>
+  <si>
+    <t>Not Executed</t>
   </si>
   <si>
     <t>HOM-SCN-02</t>
@@ -1023,6 +1161,12 @@
     <t>The Explore India section should render correctly and be visible on the page.</t>
   </si>
   <si>
+    <t>4596 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:01 PM</t>
+  </si>
+  <si>
     <t>BLOG-SCN-02</t>
   </si>
   <si>
@@ -1041,10 +1185,10 @@
     <t>The Blogs section should render correctly with visible blog entries.</t>
   </si>
   <si>
-    <t>TimeoutError: locator.click: Timeout 10000ms exceeded.</t>
-  </si>
-  <si>
-    <t>Fail</t>
+    <t>7872 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:09 PM</t>
   </si>
   <si>
     <t>MTW-SCN-21</t>
@@ -1071,6 +1215,12 @@
     <t>Verify that on cancelling an eligible booking, the system should change status to Cancelled once and display applicable refund details.</t>
   </si>
   <si>
+    <t>204 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:05 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-22</t>
   </si>
   <si>
@@ -1091,6 +1241,9 @@
     <t>Verify that displayed refund data should match the cancelled booking and its payment record.</t>
   </si>
   <si>
+    <t>243 ms</t>
+  </si>
+  <si>
     <t>MTW-SCN-23</t>
   </si>
   <si>
@@ -1112,6 +1265,9 @@
   </si>
   <si>
     <t>Order ID observed in PayU flow, e.g. MTPAYU_4c3b3ce733f2258874.</t>
+  </si>
+  <si>
+    <t>211 ms</t>
   </si>
   <si>
     <t>MTW-SCN-24</t>
@@ -1135,6 +1291,12 @@
     <t>Verify that with the 'Reserve with small advance' option, the system should create a reservation for the stated advance and show the remaining balance as payable at the property.</t>
   </si>
   <si>
+    <t>23106 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:13 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-25</t>
   </si>
   <si>
@@ -1156,6 +1318,12 @@
     <t>Verify that on generating the UPI QR, the system should display a scannable QR with a payment sub-timer and poll for status, handling the pending and expiry states safely.</t>
   </si>
   <si>
+    <t>24847 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:37 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-26</t>
   </si>
   <si>
@@ -1177,6 +1345,12 @@
     <t>Verify that the Cards path should hand off to the PayU gateway, generate a unique Order ID, and surface PCI DSS compliance without creating duplicate orders.</t>
   </si>
   <si>
+    <t>377 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:38 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-27</t>
   </si>
   <si>
@@ -1198,6 +1372,9 @@
     <t>Verify that Net Banking should present a searchable bank list and enable Pay Now only once a bank is selected.</t>
   </si>
   <si>
+    <t>752 ms</t>
+  </si>
+  <si>
     <t>MTW-SCN-28</t>
   </si>
   <si>
@@ -1219,6 +1396,9 @@
     <t>Verify that Wallet should present a searchable wallet list and enable Pay with Wallet only once a wallet is selected.</t>
   </si>
   <si>
+    <t>472 ms</t>
+  </si>
+  <si>
     <t>MTW-SCN-29</t>
   </si>
   <si>
@@ -1240,6 +1420,12 @@
     <t>Verify that editing guest details from the payment step should update the summary while preserving the room hold and booking context.</t>
   </si>
   <si>
+    <t>22401 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:56:02 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-30</t>
   </si>
   <si>
@@ -1260,6 +1446,12 @@
     <t>Verify that the Share action should open a share modal with social options and a copy-link control without changing the page or booking state.</t>
   </si>
   <si>
+    <t>17112 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:14 PM</t>
+  </si>
+  <si>
     <t>■  NEGATIVE FLOW  —  Verifying error handling and edge cases (10 cases)</t>
   </si>
   <si>
@@ -1283,6 +1475,12 @@
     <t>Verify that on tapping Search with no location, the system should display a clear inline validation message on the Where field.</t>
   </si>
   <si>
+    <t>2738 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:21 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-32</t>
   </si>
   <si>
@@ -1300,6 +1498,9 @@
   </si>
   <si>
     <t>Verify that on payment failure or timeout, the system should show a clear error, release the hold safely, and allow retry.</t>
+  </si>
+  <si>
+    <t>28224 ms</t>
   </si>
   <si>
     <t>PAY-SCN-03</t>
@@ -1323,7 +1524,10 @@
     <t>The email field should fail HTML5 validity (checkValidity() = false) and block submission.</t>
   </si>
   <si>
-    <t>Email field validity check correctly returned false on all three browsers; submission blocked.</t>
+    <t>7722 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:56:10 PM</t>
   </si>
   <si>
     <t>PAY-SCN-04</t>
@@ -1346,10 +1550,13 @@
     <t>If the coupon field is present, an 'invalid/expired/not applicable' message should be shown. If absent, the test should skip gracefully rather than fail.</t>
   </si>
   <si>
-    <t>Coupon field was not present for the room selection used, so the graceful-skip branch was exercised without error; test completed successfully.</t>
-  </si>
-  <si>
     <t>Also covers former MTW-TC-12 (invalid coupon rejection).</t>
+  </si>
+  <si>
+    <t>10649 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:56:20 PM</t>
   </si>
   <si>
     <t>MTW-SCN-33</t>
@@ -1369,6 +1576,9 @@
   </si>
   <si>
     <t>Verify that with a prohibited or duplicate cancellation, the system should block the action and show policy guidance.</t>
+  </si>
+  <si>
+    <t>236 ms</t>
   </si>
   <si>
     <t>MTW-SCN-34</t>
@@ -1388,6 +1598,12 @@
     <t>Verify that with invalid phone values, the system should reject the input without corrupting the country code.</t>
   </si>
   <si>
+    <t>18380 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:22 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-35</t>
   </si>
   <si>
@@ -1408,6 +1624,9 @@
     <t>Verify that company and GST fields should appear as optional and should not block checkout when left empty.</t>
   </si>
   <si>
+    <t>19684 ms</t>
+  </si>
+  <si>
     <t>MTW-SCN-36</t>
   </si>
   <si>
@@ -1428,6 +1647,12 @@
     <t>Verify that after a cancelled or failed payment, the booking should remain unpaid with a safe retry path available.</t>
   </si>
   <si>
+    <t>412 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:43 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-37</t>
   </si>
   <si>
@@ -1448,6 +1673,9 @@
     <t>Verify that on an uncertain timeout, the system should reconcile payment status before retry and prevent duplicate charging.</t>
   </si>
   <si>
+    <t>221 ms</t>
+  </si>
+  <si>
     <t>MTW-SCN-38</t>
   </si>
   <si>
@@ -1493,7 +1721,16 @@
     <t>Error: [2mexpect([22m[31mlocator[39m[2m).not.[22mtoBeVisible[2m([22m[2m)[22m failed</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>Broken link on a valid navigation path; support content is unreachable.</t>
+  </si>
+  <si>
+    <t>16478 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:13 PM</t>
   </si>
   <si>
     <t>MTW-SCN-40</t>
@@ -1520,6 +1757,12 @@
     <t>Error: [2mexpect([22m[31mlocator[39m[2m).[22mtoBeVisible[2m([22m[2m)[22m failed</t>
   </si>
   <si>
+    <t>9836 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:07 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-41</t>
   </si>
   <si>
@@ -1538,6 +1781,9 @@
   </si>
   <si>
     <t>Verify that with a guest aged 17y 11m, the system should classify the guest as CHILD per a defined boundary rule.</t>
+  </si>
+  <si>
+    <t>0 ms</t>
   </si>
   <si>
     <t>MTW-SCN-42</t>
@@ -1607,6 +1853,9 @@
     <t>Verify that with a check-in date that expires during the hold, the server should re-validate at submission and block the now-past date.</t>
   </si>
   <si>
+    <t>27610 ms</t>
+  </si>
+  <si>
     <t>MTW-SCN-45</t>
   </si>
   <si>
@@ -1633,6 +1882,12 @@
     <t>Distinct from MTW-TC-72: this is timer reset on refresh; TC-72 is controls left enabled after expiry.</t>
   </si>
   <si>
+    <t>20616 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:45 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-46</t>
   </si>
   <si>
@@ -1656,6 +1911,12 @@
   </si>
   <si>
     <t>CONFLICT: automation TC3 reports Pass for invalid email. Manual test used a structurally valid but non-existent domain (asdsgsi@sdhd.dj). Reconcile scope before sign-off.</t>
+  </si>
+  <si>
+    <t>24567 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:10 PM</t>
   </si>
   <si>
     <t>MTW-SCN-47</t>
@@ -1681,6 +1942,12 @@
     <t>Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoBeLessThan[2m([22m[32mexpected[39m[2m)[22m</t>
   </si>
   <si>
+    <t>17831 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:27 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-48</t>
   </si>
   <si>
@@ -1702,6 +1969,12 @@
   </si>
   <si>
     <t>Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m</t>
+  </si>
+  <si>
+    <t>12362 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:55:40 PM</t>
   </si>
   <si>
     <t>MTW-SCN-49</t>
@@ -1725,6 +1998,9 @@
     <t>Verify that payment selectors should be keyboard-focusable with accessible names, visible focus states, keyboard activation and a selected state.</t>
   </si>
   <si>
+    <t>7/31/2026, 2:53:56 PM</t>
+  </si>
+  <si>
     <t>MTW-SCN-50</t>
   </si>
   <si>
@@ -1766,6 +2042,12 @@
   </si>
   <si>
     <t>Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoMatch[2m([22m[32mexpected[39m[2m)[22m</t>
+  </si>
+  <si>
+    <t>7738 ms</t>
+  </si>
+  <si>
+    <t>7/31/2026, 2:54:04 PM</t>
   </si>
   <si>
     <t>MTW-SCN-52</t>
@@ -1787,6 +2069,12 @@
   </si>
   <si>
     <t>Verify that on continuing to checkout, the system should preserve the exact selected room name, occupancy and rate.</t>
+  </si>
+  <si>
+    <t>TimeoutError: locator.click: Timeout 10000ms exceeded.</t>
+  </si>
+  <si>
+    <t>12583 ms</t>
   </si>
   <si>
     <t>MTW-SCN-53</t>
@@ -2238,7 +2526,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3039,8 +3327,12 @@
       <c r="L12" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
+      <c r="M12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>40</v>
+      </c>
       <c r="O12" s="21"/>
       <c r="P12" s="21"/>
       <c r="Q12" s="21"/>
@@ -3057,25 +3349,25 @@
     </row>
     <row r="13" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H13" s="22" t="s">
         <v>34</v>
@@ -3086,10 +3378,14 @@
       <c r="J13" s="22"/>
       <c r="K13" s="25"/>
       <c r="L13" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
@@ -3106,25 +3402,25 @@
     </row>
     <row r="14" ht="116" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>34</v>
@@ -3136,13 +3432,17 @@
         <v>36</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L14" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="O14" s="21"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
@@ -3159,25 +3459,25 @@
     </row>
     <row r="15" ht="116" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H15" s="22" t="s">
         <v>34</v>
@@ -3187,13 +3487,17 @@
       </c>
       <c r="J15" s="22"/>
       <c r="K15" s="25" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L15" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
+      <c r="M15" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
@@ -3210,25 +3514,25 @@
     </row>
     <row r="16" ht="116" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H16" s="16" t="s">
         <v>34</v>
@@ -3238,13 +3542,17 @@
       </c>
       <c r="J16" s="16"/>
       <c r="K16" s="19" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L16" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>76</v>
+      </c>
       <c r="O16" s="21"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
@@ -3261,25 +3569,25 @@
     </row>
     <row r="17" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H17" s="22" t="s">
         <v>34</v>
@@ -3294,8 +3602,12 @@
       <c r="L17" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
+      <c r="M17" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>85</v>
+      </c>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
@@ -3312,25 +3624,25 @@
     </row>
     <row r="18" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H18" s="16" t="s">
         <v>34</v>
@@ -3343,8 +3655,12 @@
       <c r="L18" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
+      <c r="M18" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="N18" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="O18" s="21"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="21"/>
@@ -3361,25 +3677,25 @@
     </row>
     <row r="19" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H19" s="22" t="s">
         <v>34</v>
@@ -3392,8 +3708,12 @@
       <c r="L19" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
+      <c r="M19" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
@@ -3410,25 +3730,25 @@
     </row>
     <row r="20" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H20" s="16" t="s">
         <v>34</v>
@@ -3439,10 +3759,14 @@
       <c r="J20" s="16"/>
       <c r="K20" s="19"/>
       <c r="L20" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
+        <v>47</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>109</v>
+      </c>
       <c r="O20" s="21"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
@@ -3459,25 +3783,25 @@
     </row>
     <row r="21" ht="183.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="H21" s="22" t="s">
         <v>34</v>
@@ -3490,8 +3814,12 @@
       <c r="L21" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
+      <c r="M21" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>118</v>
+      </c>
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
@@ -3508,25 +3836,25 @@
     </row>
     <row r="22" ht="197" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>34</v>
@@ -3537,10 +3865,14 @@
       <c r="J22" s="16"/>
       <c r="K22" s="19"/>
       <c r="L22" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="N22" s="21" t="s">
+        <v>126</v>
+      </c>
       <c r="O22" s="21"/>
       <c r="P22" s="21"/>
       <c r="Q22" s="21"/>
@@ -3557,25 +3889,25 @@
     </row>
     <row r="23" ht="170" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="H23" s="22" t="s">
         <v>34</v>
@@ -3586,10 +3918,14 @@
       <c r="J23" s="22"/>
       <c r="K23" s="25"/>
       <c r="L23" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>134</v>
+      </c>
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
@@ -3606,25 +3942,25 @@
     </row>
     <row r="24" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>34</v>
@@ -3636,13 +3972,17 @@
         <v>36</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="L24" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
+      <c r="M24" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>144</v>
+      </c>
       <c r="O24" s="21"/>
       <c r="P24" s="21"/>
       <c r="Q24" s="21"/>
@@ -3659,25 +3999,25 @@
     </row>
     <row r="25" ht="143" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>34</v>
@@ -3687,14 +4027,20 @@
       </c>
       <c r="J25" s="22"/>
       <c r="K25" s="25" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="L25" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>155</v>
+      </c>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
       <c r="R25" s="11"/>
@@ -3710,39 +4056,43 @@
     </row>
     <row r="26" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J26" s="16"/>
       <c r="K26" s="19"/>
       <c r="L26" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>154</v>
+      </c>
       <c r="O26" s="21"/>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
@@ -3759,25 +4109,25 @@
     </row>
     <row r="27" ht="260" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="H27" s="22" t="s">
         <v>34</v>
@@ -3787,13 +4137,17 @@
       </c>
       <c r="J27" s="22"/>
       <c r="K27" s="25" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="L27" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
+      <c r="M27" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>173</v>
+      </c>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
@@ -3810,25 +4164,25 @@
     </row>
     <row r="28" ht="102.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="H28" s="16" t="s">
         <v>34</v>
@@ -3841,8 +4195,12 @@
       <c r="L28" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
+      <c r="M28" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>182</v>
+      </c>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
@@ -3859,25 +4217,25 @@
     </row>
     <row r="29" ht="197" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="H29" s="22" t="s">
         <v>34</v>
@@ -3887,13 +4245,17 @@
       </c>
       <c r="J29" s="22"/>
       <c r="K29" s="25" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="L29" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>192</v>
+      </c>
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
@@ -3910,25 +4272,25 @@
     </row>
     <row r="30" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>34</v>
@@ -3938,13 +4300,17 @@
       </c>
       <c r="J30" s="16"/>
       <c r="K30" s="19" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="L30" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+        <v>47</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="N30" s="21" t="s">
+        <v>201</v>
+      </c>
       <c r="O30" s="21"/>
       <c r="P30" s="21"/>
       <c r="Q30" s="21"/>
@@ -3961,25 +4327,25 @@
     </row>
     <row r="31" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="H31" s="22" t="s">
         <v>34</v>
@@ -3989,13 +4355,17 @@
       </c>
       <c r="J31" s="22"/>
       <c r="K31" s="25" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="L31" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>210</v>
+      </c>
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
@@ -4012,43 +4382,47 @@
     </row>
     <row r="32" ht="102.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>176</v>
+        <v>216</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="L32" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="N32" s="21" t="s">
+        <v>221</v>
+      </c>
       <c r="O32" s="21"/>
       <c r="P32" s="21"/>
       <c r="Q32" s="21"/>
@@ -4065,43 +4439,47 @@
     </row>
     <row r="33" ht="89" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="J33" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K33" s="25" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="L33" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
+      <c r="M33" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>230</v>
+      </c>
       <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
@@ -4118,43 +4496,47 @@
     </row>
     <row r="34" ht="170" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>197</v>
+        <v>34</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="J34" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L34" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
+      <c r="M34" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>240</v>
+      </c>
       <c r="O34" s="21"/>
       <c r="P34" s="21"/>
       <c r="Q34" s="21"/>
@@ -4171,43 +4553,47 @@
     </row>
     <row r="35" ht="102.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="J35" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K35" s="25" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L35" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="N35" s="11" t="s">
+        <v>248</v>
+      </c>
       <c r="O35" s="11"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
@@ -4224,43 +4610,47 @@
     </row>
     <row r="36" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>212</v>
+        <v>34</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="J36" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="L36" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
+      <c r="M36" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="N36" s="21" t="s">
+        <v>257</v>
+      </c>
       <c r="O36" s="21"/>
       <c r="P36" s="21"/>
       <c r="Q36" s="21"/>
@@ -4277,43 +4667,47 @@
     </row>
     <row r="37" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="F37" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="G37" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="H37" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="J37" s="22" t="s">
-        <v>180</v>
-      </c>
       <c r="K37" s="25" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="L37" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
+      <c r="M37" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="N37" s="11" t="s">
+        <v>266</v>
+      </c>
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
@@ -4330,40 +4724,40 @@
     </row>
     <row r="38" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>227</v>
+        <v>272</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>228</v>
+        <v>273</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>229</v>
+        <v>274</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J38" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K38" s="19" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L38" s="27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M38" s="21"/>
       <c r="N38" s="21"/>
@@ -4383,40 +4777,40 @@
     </row>
     <row r="39" ht="102.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J39" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K39" s="25" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L39" s="34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
@@ -4436,37 +4830,37 @@
     </row>
     <row r="40" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J40" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K40" s="19" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="L40" s="20" t="s">
         <v>38</v>
@@ -4489,37 +4883,37 @@
     </row>
     <row r="41" ht="89" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="E41" s="22" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J41" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K41" s="25" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L41" s="28" t="s">
         <v>38</v>
@@ -4542,37 +4936,37 @@
     </row>
     <row r="42" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>253</v>
+        <v>299</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J42" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K42" s="19" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L42" s="20" t="s">
         <v>38</v>
@@ -4595,40 +4989,40 @@
     </row>
     <row r="43" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>260</v>
+        <v>306</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="I43" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J43" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K43" s="25" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L43" s="26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M43" s="11"/>
       <c r="N43" s="11"/>
@@ -4648,40 +5042,40 @@
     </row>
     <row r="44" ht="89" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J44" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K44" s="19" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
       <c r="L44" s="27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M44" s="21"/>
       <c r="N44" s="21"/>
@@ -4701,40 +5095,40 @@
     </row>
     <row r="45" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="C45" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="B45" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>224</v>
-      </c>
       <c r="D45" s="15" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="I45" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J45" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K45" s="25" t="s">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="L45" s="34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M45" s="11"/>
       <c r="N45" s="11"/>
@@ -4754,37 +5148,37 @@
     </row>
     <row r="46" ht="102.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="I46" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="H46" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="I46" s="18" t="s">
-        <v>179</v>
-      </c>
       <c r="J46" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K46" s="19" t="s">
-        <v>280</v>
+        <v>326</v>
       </c>
       <c r="L46" s="20" t="s">
         <v>38</v>
@@ -4807,37 +5201,37 @@
     </row>
     <row r="47" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J47" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K47" s="25" t="s">
-        <v>287</v>
+        <v>333</v>
       </c>
       <c r="L47" s="28" t="s">
         <v>38</v>
@@ -4860,40 +5254,40 @@
     </row>
     <row r="48" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>291</v>
+        <v>337</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>293</v>
+        <v>339</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J48" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K48" s="19" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L48" s="29" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M48" s="21"/>
       <c r="N48" s="21"/>
@@ -4913,40 +5307,40 @@
     </row>
     <row r="49" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>295</v>
+        <v>341</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>296</v>
+        <v>342</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>297</v>
+        <v>343</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>301</v>
+        <v>347</v>
       </c>
       <c r="I49" s="18" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J49" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K49" s="25" t="s">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="L49" s="26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M49" s="11"/>
       <c r="N49" s="11"/>
@@ -4966,25 +5360,25 @@
     </row>
     <row r="50" ht="89" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>303</v>
+        <v>349</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>307</v>
+        <v>353</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>308</v>
+        <v>354</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>34</v>
@@ -4993,16 +5387,20 @@
         <v>35</v>
       </c>
       <c r="J50" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K50" s="19" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L50" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M50" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="N50" s="21" t="s">
+        <v>357</v>
+      </c>
       <c r="O50" s="21"/>
       <c r="P50" s="21"/>
       <c r="Q50" s="21"/>
@@ -5019,43 +5417,47 @@
     </row>
     <row r="51" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>316</v>
+        <v>34</v>
       </c>
       <c r="I51" s="18" t="s">
-        <v>317</v>
+        <v>35</v>
       </c>
       <c r="J51" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K51" s="25" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L51" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
+        <v>57</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>365</v>
+      </c>
       <c r="O51" s="11"/>
       <c r="P51" s="11"/>
       <c r="Q51" s="11"/>
@@ -5072,39 +5474,43 @@
     </row>
     <row r="52" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="35" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>323</v>
+        <v>371</v>
       </c>
       <c r="G52" s="16" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="H52" s="16" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J52" s="16"/>
       <c r="K52" s="19"/>
       <c r="L52" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M52" s="21"/>
-      <c r="N52" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M52" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="N52" s="21" t="s">
+        <v>374</v>
+      </c>
       <c r="O52" s="21"/>
       <c r="P52" s="21"/>
       <c r="Q52" s="21"/>
@@ -5121,39 +5527,43 @@
     </row>
     <row r="53" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="35" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>327</v>
+        <v>377</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>328</v>
+        <v>378</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J53" s="22"/>
       <c r="K53" s="25"/>
       <c r="L53" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
+      <c r="M53" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>374</v>
+      </c>
       <c r="O53" s="11"/>
       <c r="P53" s="11"/>
       <c r="Q53" s="11"/>
@@ -5170,41 +5580,45 @@
     </row>
     <row r="54" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>334</v>
+        <v>385</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J54" s="16"/>
       <c r="K54" s="19" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="L54" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
+        <v>152</v>
+      </c>
+      <c r="M54" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="N54" s="21" t="s">
+        <v>374</v>
+      </c>
       <c r="O54" s="21"/>
       <c r="P54" s="21"/>
       <c r="Q54" s="21"/>
@@ -5221,25 +5635,25 @@
     </row>
     <row r="55" ht="143" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>339</v>
+        <v>391</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>340</v>
+        <v>392</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>343</v>
+        <v>395</v>
       </c>
       <c r="H55" s="22" t="s">
         <v>34</v>
@@ -5250,10 +5664,14 @@
       <c r="J55" s="22"/>
       <c r="K55" s="25"/>
       <c r="L55" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
+        <v>57</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>397</v>
+      </c>
       <c r="O55" s="11"/>
       <c r="P55" s="11"/>
       <c r="Q55" s="11"/>
@@ -5270,25 +5688,25 @@
     </row>
     <row r="56" ht="156.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>346</v>
+        <v>400</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="G56" s="16" t="s">
-        <v>349</v>
+        <v>403</v>
       </c>
       <c r="H56" s="16" t="s">
         <v>34</v>
@@ -5299,8 +5717,12 @@
       <c r="J56" s="16"/>
       <c r="K56" s="19"/>
       <c r="L56" s="15"/>
-      <c r="M56" s="21"/>
-      <c r="N56" s="21"/>
+      <c r="M56" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="N56" s="21" t="s">
+        <v>405</v>
+      </c>
       <c r="O56" s="21"/>
       <c r="P56" s="21"/>
       <c r="Q56" s="21"/>
@@ -5317,25 +5739,25 @@
     </row>
     <row r="57" ht="156.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
-        <v>350</v>
+        <v>406</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>351</v>
+        <v>407</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>352</v>
+        <v>408</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>353</v>
+        <v>409</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>354</v>
+        <v>410</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>355</v>
+        <v>411</v>
       </c>
       <c r="H57" s="22" t="s">
         <v>34</v>
@@ -5346,8 +5768,12 @@
       <c r="J57" s="22"/>
       <c r="K57" s="25"/>
       <c r="L57" s="15"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
+      <c r="M57" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="N57" s="11" t="s">
+        <v>413</v>
+      </c>
       <c r="O57" s="11"/>
       <c r="P57" s="11"/>
       <c r="Q57" s="11"/>
@@ -5364,25 +5790,25 @@
     </row>
     <row r="58" ht="156.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
-        <v>356</v>
+        <v>414</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="H58" s="16" t="s">
         <v>34</v>
@@ -5393,8 +5819,12 @@
       <c r="J58" s="16"/>
       <c r="K58" s="19"/>
       <c r="L58" s="15"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="21"/>
+      <c r="M58" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="N58" s="21" t="s">
+        <v>240</v>
+      </c>
       <c r="O58" s="21"/>
       <c r="P58" s="21"/>
       <c r="Q58" s="21"/>
@@ -5411,25 +5841,25 @@
     </row>
     <row r="59" ht="156.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
-        <v>362</v>
+        <v>421</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>363</v>
+        <v>422</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>366</v>
+        <v>425</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="H59" s="22" t="s">
         <v>34</v>
@@ -5440,8 +5870,12 @@
       <c r="J59" s="22"/>
       <c r="K59" s="25"/>
       <c r="L59" s="15"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
+      <c r="M59" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="N59" s="11" t="s">
+        <v>240</v>
+      </c>
       <c r="O59" s="11"/>
       <c r="P59" s="11"/>
       <c r="Q59" s="11"/>
@@ -5458,25 +5892,25 @@
     </row>
     <row r="60" ht="156.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="H60" s="16" t="s">
         <v>34</v>
@@ -5487,8 +5921,12 @@
       <c r="J60" s="16"/>
       <c r="K60" s="19"/>
       <c r="L60" s="15"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="21"/>
+      <c r="M60" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="N60" s="21" t="s">
+        <v>435</v>
+      </c>
       <c r="O60" s="21"/>
       <c r="P60" s="21"/>
       <c r="Q60" s="21"/>
@@ -5505,25 +5943,25 @@
     </row>
     <row r="61" ht="143" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
-        <v>374</v>
+        <v>436</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>375</v>
+        <v>437</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>376</v>
+        <v>438</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>377</v>
+        <v>439</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>378</v>
+        <v>440</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>379</v>
+        <v>441</v>
       </c>
       <c r="H61" s="22" t="s">
         <v>34</v>
@@ -5534,10 +5972,14 @@
       <c r="J61" s="22"/>
       <c r="K61" s="25"/>
       <c r="L61" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="N61" s="11" t="s">
+        <v>443</v>
+      </c>
       <c r="O61" s="11"/>
       <c r="P61" s="11"/>
       <c r="Q61" s="11"/>
@@ -5554,7 +5996,7 @@
     </row>
     <row r="62" ht="28" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>380</v>
+        <v>444</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -5585,25 +6027,25 @@
     </row>
     <row r="63" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>382</v>
+        <v>446</v>
       </c>
       <c r="C63" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>386</v>
+        <v>450</v>
       </c>
       <c r="H63" s="22" t="s">
         <v>34</v>
@@ -5618,8 +6060,12 @@
       <c r="L63" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M63" s="11"/>
-      <c r="N63" s="11"/>
+      <c r="M63" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="N63" s="11" t="s">
+        <v>452</v>
+      </c>
       <c r="O63" s="11"/>
       <c r="P63" s="11"/>
       <c r="Q63" s="11"/>
@@ -5636,25 +6082,25 @@
     </row>
     <row r="64" ht="116" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
-        <v>387</v>
+        <v>453</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>388</v>
+        <v>454</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>389</v>
+        <v>455</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>390</v>
+        <v>456</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>391</v>
+        <v>457</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>392</v>
+        <v>458</v>
       </c>
       <c r="H64" s="16" t="s">
         <v>34</v>
@@ -5665,10 +6111,14 @@
       <c r="J64" s="16"/>
       <c r="K64" s="19"/>
       <c r="L64" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M64" s="21"/>
-      <c r="N64" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M64" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="N64" s="21" t="s">
+        <v>67</v>
+      </c>
       <c r="O64" s="21"/>
       <c r="P64" s="21"/>
       <c r="Q64" s="21"/>
@@ -5685,43 +6135,47 @@
     </row>
     <row r="65" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
-        <v>393</v>
+        <v>460</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>394</v>
+        <v>461</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>395</v>
+        <v>462</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>396</v>
+        <v>463</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>397</v>
+        <v>464</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>398</v>
+        <v>465</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>399</v>
+        <v>34</v>
       </c>
       <c r="I65" s="18" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="J65" s="22" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="L65" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
+      <c r="M65" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="N65" s="11" t="s">
+        <v>467</v>
+      </c>
       <c r="O65" s="11"/>
       <c r="P65" s="11"/>
       <c r="Q65" s="11"/>
@@ -5738,43 +6192,47 @@
     </row>
     <row r="66" ht="89" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
-        <v>400</v>
+        <v>468</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>401</v>
+        <v>469</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>402</v>
+        <v>470</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>403</v>
+        <v>471</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>404</v>
+        <v>472</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>405</v>
+        <v>473</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>406</v>
+        <v>162</v>
       </c>
       <c r="I66" s="18" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="J66" s="16" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>407</v>
+        <v>474</v>
       </c>
       <c r="L66" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="M66" s="21"/>
-      <c r="N66" s="21"/>
+        <v>47</v>
+      </c>
+      <c r="M66" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="N66" s="21" t="s">
+        <v>476</v>
+      </c>
       <c r="O66" s="21"/>
       <c r="P66" s="21"/>
       <c r="Q66" s="21"/>
@@ -5791,39 +6249,43 @@
     </row>
     <row r="67" ht="62" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
-        <v>408</v>
+        <v>477</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>409</v>
+        <v>478</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>411</v>
+        <v>480</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>412</v>
+        <v>481</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J67" s="22"/>
       <c r="K67" s="25"/>
       <c r="L67" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M67" s="11"/>
-      <c r="N67" s="11"/>
+      <c r="M67" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="N67" s="11" t="s">
+        <v>210</v>
+      </c>
       <c r="O67" s="11"/>
       <c r="P67" s="11"/>
       <c r="Q67" s="11"/>
@@ -5840,25 +6302,25 @@
     </row>
     <row r="68" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
-        <v>414</v>
+        <v>484</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>415</v>
+        <v>485</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>416</v>
+        <v>486</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>417</v>
+        <v>487</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>418</v>
+        <v>488</v>
       </c>
       <c r="H68" s="16" t="s">
         <v>34</v>
@@ -5871,8 +6333,12 @@
       <c r="L68" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
+      <c r="M68" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="N68" s="21" t="s">
+        <v>490</v>
+      </c>
       <c r="O68" s="21"/>
       <c r="P68" s="21"/>
       <c r="Q68" s="21"/>
@@ -5889,25 +6355,25 @@
     </row>
     <row r="69" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
-        <v>419</v>
+        <v>491</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>420</v>
+        <v>492</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>421</v>
+        <v>493</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>422</v>
+        <v>494</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>423</v>
+        <v>495</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>424</v>
+        <v>496</v>
       </c>
       <c r="H69" s="22" t="s">
         <v>34</v>
@@ -5918,10 +6384,14 @@
       <c r="J69" s="22"/>
       <c r="K69" s="25"/>
       <c r="L69" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="N69" s="11" t="s">
+        <v>248</v>
+      </c>
       <c r="O69" s="11"/>
       <c r="P69" s="11"/>
       <c r="Q69" s="11"/>
@@ -5938,25 +6408,25 @@
     </row>
     <row r="70" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="31" t="s">
-        <v>425</v>
+        <v>498</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>426</v>
+        <v>499</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>427</v>
+        <v>500</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>428</v>
+        <v>501</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>429</v>
+        <v>502</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>430</v>
+        <v>503</v>
       </c>
       <c r="H70" s="16" t="s">
         <v>34</v>
@@ -5967,10 +6437,14 @@
       <c r="J70" s="16"/>
       <c r="K70" s="19"/>
       <c r="L70" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M70" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="N70" s="21" t="s">
+        <v>505</v>
+      </c>
       <c r="O70" s="21"/>
       <c r="P70" s="21"/>
       <c r="Q70" s="21"/>
@@ -5987,25 +6461,25 @@
     </row>
     <row r="71" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
-        <v>431</v>
+        <v>506</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>432</v>
+        <v>507</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>433</v>
+        <v>508</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>434</v>
+        <v>509</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>435</v>
+        <v>510</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>436</v>
+        <v>511</v>
       </c>
       <c r="H71" s="22" t="s">
         <v>34</v>
@@ -6016,10 +6490,14 @@
       <c r="J71" s="22"/>
       <c r="K71" s="25"/>
       <c r="L71" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="N71" s="11" t="s">
+        <v>505</v>
+      </c>
       <c r="O71" s="11"/>
       <c r="P71" s="11"/>
       <c r="Q71" s="11"/>
@@ -6036,25 +6514,25 @@
     </row>
     <row r="72" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>439</v>
+        <v>515</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>440</v>
+        <v>516</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>441</v>
+        <v>517</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>442</v>
+        <v>518</v>
       </c>
       <c r="H72" s="16" t="s">
         <v>34</v>
@@ -6065,10 +6543,14 @@
       <c r="J72" s="16"/>
       <c r="K72" s="19"/>
       <c r="L72" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
+        <v>152</v>
+      </c>
+      <c r="M72" s="21" t="s">
+        <v>512</v>
+      </c>
+      <c r="N72" s="21" t="s">
+        <v>505</v>
+      </c>
       <c r="O72" s="21"/>
       <c r="P72" s="21"/>
       <c r="Q72" s="21"/>
@@ -6085,7 +6567,7 @@
     </row>
     <row r="73" ht="28" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -6116,42 +6598,48 @@
     </row>
     <row r="74" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>446</v>
+        <v>522</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>449</v>
+        <v>525</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>450</v>
+        <v>526</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J74" s="16"/>
       <c r="K74" s="19" t="s">
-        <v>451</v>
+        <v>528</v>
       </c>
       <c r="L74" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
+      <c r="M74" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="N74" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="O74" s="21" t="s">
+        <v>526</v>
+      </c>
       <c r="P74" s="21"/>
       <c r="Q74" s="21"/>
       <c r="R74" s="21"/>
@@ -6167,42 +6655,48 @@
     </row>
     <row r="75" ht="89" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="32" t="s">
-        <v>452</v>
+        <v>531</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>453</v>
+        <v>532</v>
       </c>
       <c r="C75" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>454</v>
+        <v>533</v>
       </c>
       <c r="E75" s="22" t="s">
-        <v>455</v>
+        <v>534</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>457</v>
+        <v>536</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>458</v>
+        <v>537</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J75" s="22" t="s">
         <v>36</v>
       </c>
       <c r="K75" s="25"/>
       <c r="L75" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="M75" s="11"/>
-      <c r="N75" s="11"/>
-      <c r="O75" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>538</v>
+      </c>
+      <c r="N75" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="O75" s="11" t="s">
+        <v>537</v>
+      </c>
       <c r="P75" s="11"/>
       <c r="Q75" s="11"/>
       <c r="R75" s="11"/>
@@ -6218,41 +6712,45 @@
     </row>
     <row r="76" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
-        <v>459</v>
+        <v>540</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>460</v>
+        <v>541</v>
       </c>
       <c r="C76" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>461</v>
+        <v>542</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>462</v>
+        <v>543</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>463</v>
+        <v>544</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>464</v>
+        <v>545</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J76" s="16" t="s">
         <v>36</v>
       </c>
       <c r="K76" s="19"/>
       <c r="L76" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
+        <v>47</v>
+      </c>
+      <c r="M76" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="N76" s="21" t="s">
+        <v>539</v>
+      </c>
       <c r="O76" s="21"/>
       <c r="P76" s="21"/>
       <c r="Q76" s="21"/>
@@ -6269,43 +6767,47 @@
     </row>
     <row r="77" ht="89" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
-        <v>465</v>
+        <v>547</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>466</v>
+        <v>548</v>
       </c>
       <c r="C77" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>467</v>
+        <v>549</v>
       </c>
       <c r="E77" s="22" t="s">
-        <v>468</v>
+        <v>550</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>469</v>
+        <v>551</v>
       </c>
       <c r="G77" s="22" t="s">
-        <v>470</v>
+        <v>552</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I77" s="37" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J77" s="22" t="s">
         <v>36</v>
       </c>
       <c r="K77" s="25" t="s">
-        <v>471</v>
+        <v>553</v>
       </c>
       <c r="L77" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="M77" s="11"/>
-      <c r="N77" s="11"/>
+        <v>57</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="N77" s="11" t="s">
+        <v>539</v>
+      </c>
       <c r="O77" s="11"/>
       <c r="P77" s="11"/>
       <c r="Q77" s="11"/>
@@ -6322,43 +6824,47 @@
     </row>
     <row r="78" ht="102.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="33" t="s">
-        <v>472</v>
+        <v>554</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>473</v>
+        <v>555</v>
       </c>
       <c r="C78" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>474</v>
+        <v>556</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>475</v>
+        <v>557</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>476</v>
+        <v>558</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>477</v>
+        <v>559</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J78" s="16" t="s">
         <v>36</v>
       </c>
       <c r="K78" s="19" t="s">
-        <v>478</v>
+        <v>560</v>
       </c>
       <c r="L78" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
+      <c r="M78" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="N78" s="21" t="s">
+        <v>539</v>
+      </c>
       <c r="O78" s="21"/>
       <c r="P78" s="21"/>
       <c r="Q78" s="21"/>
@@ -6375,42 +6881,48 @@
     </row>
     <row r="79" ht="156.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>479</v>
+        <v>561</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>481</v>
+        <v>563</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>482</v>
+        <v>564</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>483</v>
+        <v>565</v>
       </c>
       <c r="G79" s="22" t="s">
-        <v>484</v>
+        <v>566</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>458</v>
+        <v>537</v>
       </c>
       <c r="I79" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J79" s="22" t="s">
         <v>36</v>
       </c>
       <c r="K79" s="25"/>
       <c r="L79" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="M79" s="11"/>
-      <c r="N79" s="11"/>
-      <c r="O79" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="N79" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="O79" s="11" t="s">
+        <v>537</v>
+      </c>
       <c r="P79" s="11"/>
       <c r="Q79" s="11"/>
       <c r="R79" s="11"/>
@@ -6426,44 +6938,50 @@
     </row>
     <row r="80" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>485</v>
+        <v>568</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>486</v>
+        <v>569</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>487</v>
+        <v>570</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>488</v>
+        <v>571</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>489</v>
+        <v>572</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>490</v>
+        <v>573</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>491</v>
+        <v>574</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J80" s="16" t="s">
         <v>36</v>
       </c>
       <c r="K80" s="19" t="s">
-        <v>492</v>
+        <v>575</v>
       </c>
       <c r="L80" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="M80" s="21"/>
-      <c r="N80" s="21"/>
-      <c r="O80" s="21"/>
+        <v>57</v>
+      </c>
+      <c r="M80" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="N80" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="O80" s="21" t="s">
+        <v>574</v>
+      </c>
       <c r="P80" s="21"/>
       <c r="Q80" s="21"/>
       <c r="R80" s="21"/>
@@ -6479,44 +6997,50 @@
     </row>
     <row r="81" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
-        <v>493</v>
+        <v>578</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>494</v>
+        <v>579</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>495</v>
+        <v>580</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>496</v>
+        <v>581</v>
       </c>
       <c r="F81" s="22" t="s">
-        <v>497</v>
+        <v>582</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>498</v>
+        <v>583</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>499</v>
+        <v>584</v>
       </c>
       <c r="I81" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J81" s="22" t="s">
         <v>36</v>
       </c>
       <c r="K81" s="25" t="s">
-        <v>500</v>
+        <v>585</v>
       </c>
       <c r="L81" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M81" s="11"/>
-      <c r="N81" s="11"/>
-      <c r="O81" s="11"/>
+      <c r="M81" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="N81" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="O81" s="11" t="s">
+        <v>584</v>
+      </c>
       <c r="P81" s="11"/>
       <c r="Q81" s="11"/>
       <c r="R81" s="11"/>
@@ -6532,31 +7056,31 @@
     </row>
     <row r="82" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
-        <v>501</v>
+        <v>588</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>502</v>
+        <v>589</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>503</v>
+        <v>590</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>504</v>
+        <v>591</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>505</v>
+        <v>592</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>506</v>
+        <v>593</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>507</v>
+        <v>594</v>
       </c>
       <c r="I82" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J82" s="16" t="s">
         <v>36</v>
@@ -6565,9 +7089,15 @@
       <c r="L82" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M82" s="21"/>
-      <c r="N82" s="21"/>
-      <c r="O82" s="21"/>
+      <c r="M82" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="N82" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="O82" s="21" t="s">
+        <v>594</v>
+      </c>
       <c r="P82" s="21"/>
       <c r="Q82" s="21"/>
       <c r="R82" s="21"/>
@@ -6583,42 +7113,48 @@
     </row>
     <row r="83" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
-        <v>508</v>
+        <v>597</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>509</v>
+        <v>598</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>510</v>
+        <v>599</v>
       </c>
       <c r="E83" s="22" t="s">
-        <v>511</v>
+        <v>600</v>
       </c>
       <c r="F83" s="22" t="s">
-        <v>512</v>
+        <v>601</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>513</v>
+        <v>602</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>514</v>
+        <v>603</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J83" s="22" t="s">
         <v>36</v>
       </c>
       <c r="K83" s="25"/>
       <c r="L83" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="M83" s="11"/>
-      <c r="N83" s="11"/>
-      <c r="O83" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="N83" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="O83" s="11" t="s">
+        <v>603</v>
+      </c>
       <c r="P83" s="11"/>
       <c r="Q83" s="11"/>
       <c r="R83" s="11"/>
@@ -6634,31 +7170,31 @@
     </row>
     <row r="84" ht="143" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>515</v>
+        <v>606</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>516</v>
+        <v>607</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>517</v>
+        <v>608</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>518</v>
+        <v>609</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>519</v>
+        <v>610</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>520</v>
+        <v>611</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I84" s="37" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J84" s="16" t="s">
         <v>36</v>
@@ -6667,8 +7203,12 @@
       <c r="L84" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M84" s="21"/>
-      <c r="N84" s="21"/>
+      <c r="M84" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="N84" s="21" t="s">
+        <v>612</v>
+      </c>
       <c r="O84" s="21"/>
       <c r="P84" s="21"/>
       <c r="Q84" s="21"/>
@@ -6685,31 +7225,31 @@
     </row>
     <row r="85" ht="75.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
-        <v>521</v>
+        <v>613</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>522</v>
+        <v>614</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>523</v>
+        <v>615</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>524</v>
+        <v>616</v>
       </c>
       <c r="F85" s="22" t="s">
-        <v>525</v>
+        <v>617</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>526</v>
+        <v>618</v>
       </c>
       <c r="H85" s="22" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J85" s="22" t="s">
         <v>36</v>
@@ -6718,8 +7258,12 @@
       <c r="L85" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M85" s="11"/>
-      <c r="N85" s="11"/>
+      <c r="M85" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="N85" s="11" t="s">
+        <v>612</v>
+      </c>
       <c r="O85" s="11"/>
       <c r="P85" s="11"/>
       <c r="Q85" s="11"/>
@@ -6736,31 +7280,31 @@
     </row>
     <row r="86" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>624</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="I86" s="37" t="s">
         <v>527</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>528</v>
-      </c>
-      <c r="C86" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>530</v>
-      </c>
-      <c r="F86" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="G86" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="H86" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="I86" s="37" t="s">
-        <v>317</v>
       </c>
       <c r="J86" s="16" t="s">
         <v>36</v>
@@ -6769,9 +7313,15 @@
       <c r="L86" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M86" s="21"/>
-      <c r="N86" s="21"/>
-      <c r="O86" s="21"/>
+      <c r="M86" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="N86" s="21" t="s">
+        <v>627</v>
+      </c>
+      <c r="O86" s="21" t="s">
+        <v>625</v>
+      </c>
       <c r="P86" s="21"/>
       <c r="Q86" s="21"/>
       <c r="R86" s="21"/>
@@ -6787,42 +7337,48 @@
     </row>
     <row r="87" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
-        <v>534</v>
+        <v>628</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>535</v>
+        <v>629</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>536</v>
+        <v>630</v>
       </c>
       <c r="E87" s="22" t="s">
-        <v>537</v>
+        <v>631</v>
       </c>
       <c r="F87" s="22" t="s">
-        <v>538</v>
+        <v>632</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>539</v>
+        <v>633</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>491</v>
+        <v>634</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>317</v>
+        <v>527</v>
       </c>
       <c r="J87" s="22" t="s">
         <v>36</v>
       </c>
       <c r="K87" s="25"/>
       <c r="L87" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="M87" s="11"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="11"/>
+        <v>152</v>
+      </c>
+      <c r="M87" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="N87" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="O87" s="11" t="s">
+        <v>634</v>
+      </c>
       <c r="P87" s="11"/>
       <c r="Q87" s="11"/>
       <c r="R87" s="11"/>
@@ -6838,31 +7394,31 @@
     </row>
     <row r="88" ht="143" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
-        <v>540</v>
+        <v>636</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>541</v>
+        <v>637</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>542</v>
+        <v>638</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>543</v>
+        <v>639</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>544</v>
+        <v>640</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>545</v>
+        <v>641</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I88" s="15" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J88" s="16" t="s">
         <v>36</v>
@@ -6871,8 +7427,12 @@
       <c r="L88" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M88" s="21"/>
-      <c r="N88" s="21"/>
+      <c r="M88" s="21" t="s">
+        <v>546</v>
+      </c>
+      <c r="N88" s="21" t="s">
+        <v>266</v>
+      </c>
       <c r="O88" s="21"/>
       <c r="P88" s="21"/>
       <c r="Q88" s="21"/>
@@ -6889,31 +7449,31 @@
     </row>
     <row r="89" ht="129.5" customHeight="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>546</v>
+        <v>642</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>547</v>
+        <v>643</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>548</v>
+        <v>644</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>549</v>
+        <v>645</v>
       </c>
       <c r="F89" s="22" t="s">
-        <v>550</v>
+        <v>646</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>551</v>
+        <v>647</v>
       </c>
       <c r="H89" s="22" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="I89" s="15" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="J89" s="22" t="s">
         <v>36</v>
@@ -6922,8 +7482,12 @@
       <c r="L89" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="M89" s="11"/>
-      <c r="N89" s="11"/>
+      <c r="M89" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="N89" s="11" t="s">
+        <v>266</v>
+      </c>
       <c r="O89" s="11"/>
       <c r="P89" s="11"/>
       <c r="Q89" s="11"/>
@@ -7027,75 +7591,75 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="B94" s="38" t="s">
-        <v>553</v>
+        <v>649</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="D94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="F94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="G94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="H94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="I94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="J94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="K94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="L94" s="38" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>554</v>
+        <v>650</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>555</v>
+        <v>651</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>556</v>
+        <v>652</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>557</v>
+        <v>653</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>558</v>
+        <v>654</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>559</v>
+        <v>655</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>560</v>
+        <v>656</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>561</v>
+        <v>657</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>38</v>
@@ -7103,189 +7667,189 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>562</v>
+        <v>658</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>563</v>
+        <v>659</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>556</v>
+        <v>652</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>564</v>
+        <v>660</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>565</v>
+        <v>661</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>566</v>
+        <v>662</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>567</v>
+        <v>663</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>561</v>
+        <v>657</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>568</v>
+        <v>664</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>569</v>
+        <v>665</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>556</v>
+        <v>652</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>570</v>
+        <v>666</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>571</v>
+        <v>667</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>572</v>
+        <v>668</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>573</v>
+        <v>669</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>561</v>
+        <v>657</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>574</v>
+        <v>670</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>575</v>
+        <v>671</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>556</v>
+        <v>652</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>576</v>
+        <v>672</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>571</v>
+        <v>667</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>577</v>
+        <v>673</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>578</v>
+        <v>674</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>561</v>
+        <v>657</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>579</v>
+        <v>675</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>580</v>
+        <v>676</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>581</v>
+        <v>677</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>582</v>
+        <v>678</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>583</v>
+        <v>679</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>584</v>
+        <v>680</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>585</v>
+        <v>681</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>561</v>
+        <v>657</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>586</v>
+        <v>682</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>587</v>
+        <v>683</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>588</v>
+        <v>684</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>589</v>
+        <v>685</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>583</v>
+        <v>679</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>590</v>
+        <v>686</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>591</v>
+        <v>687</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>561</v>
+        <v>657</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>38</v>
